--- a/StructureDefinition-inera-ehds-diagnostic-report-referral.xlsx
+++ b/StructureDefinition-inera-ehds-diagnostic-report-referral.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-diagnostic-report-referral.xlsx
+++ b/StructureDefinition-inera-ehds-diagnostic-report-referral.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-diagnostic-report-referral.xlsx
+++ b/StructureDefinition-inera-ehds-diagnostic-report-referral.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-diagnostic-report-referral.xlsx
+++ b/StructureDefinition-inera-ehds-diagnostic-report-referral.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -430,7 +430,7 @@
 </t>
   </si>
   <si>
-    <t>Källsystem HSA-id (referralOutcomeHeader.sourceSystemHSAId)</t>
+    <t>Källsystem HSA-id (referralOutcomeHeader.sourceSystemHSAId) – https://tjanstekatalogen.inera.se/Endpoint/{hsaId} (GENERAL-005)</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
